--- a/Tables/Data/item.xlsx
+++ b/Tables/Data/item.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -441,6 +441,7 @@
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -474,6 +475,16 @@
           <t>tags</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -504,6 +515,16 @@
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>标签，英文逗号分隔</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>描述（可空）</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>类别（Material/Consumable/Clue/Key）</t>
         </is>
       </c>
     </row>
@@ -529,6 +550,16 @@
           <t>武器,近战</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>一把普通的铁剑，刃口有些钝了。</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="B4" t="n">
@@ -552,6 +583,16 @@
           <t>武器,近战,锻造</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>锻造精良的长剑，剑身映得出人影。</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="n">
@@ -575,6 +616,16 @@
           <t>防具,重甲</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>用龙鳞缀成的护甲，沉得几乎穿不动。</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="B6" t="n">
@@ -596,6 +647,82 @@
       <c r="F6" t="inlineStr">
         <is>
           <t>消耗品,回复</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>喝下去能缓过一口气。</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Consumable</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="n">
+        <v>1005</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>破旧信笺</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>线索</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>字迹被水泡开，只认得出『镜』字</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Clue</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>1006</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>铜镜碎片</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>关键物</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>边缘还留着半个铭文</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Key</t>
         </is>
       </c>
     </row>
